--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487173_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487173_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>13.8299</v>
+        <v>11.8846</v>
       </c>
       <c r="E2" t="n">
-        <v>10.5297</v>
+        <v>9.146599999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>3.3002</v>
+        <v>2.738</v>
       </c>
       <c r="G2" t="n">
         <v>6.1819</v>
@@ -610,13 +610,13 @@
         <v>4.0532</v>
       </c>
       <c r="S2" t="n">
-        <v>3.069</v>
+        <v>1.1237</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3154</v>
+        <v>-0.0677</v>
       </c>
       <c r="U2" t="n">
-        <v>1.7535</v>
+        <v>1.1914</v>
       </c>
       <c r="V2" t="n">
         <v>2.4559</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. TRUEBA TAMAYO</t>
+          <t>H. SAIZ-BUSTAMANTE GOMEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.2375</v>
+        <v>0.0404</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0905</v>
+        <v>-1.9631</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1471</v>
+        <v>2.0034</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.5819</v>
+        <v>-1.6631</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0921</v>
+        <v>2.4332</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.674</v>
+        <v>-4.0963</v>
       </c>
       <c r="J3" t="n">
-        <v>0.326</v>
+        <v>-0.6228</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9936</v>
+        <v>2.6338</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6676</v>
+        <v>-3.2566</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.9079</v>
+        <v>-1.0403</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9014</v>
+        <v>-0.2006</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0064</v>
+        <v>-0.8397</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.386</v>
+        <v>0.965</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R3" t="n">
-        <v>0.579</v>
+        <v>2.8951</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7304</v>
+        <v>-0.5318000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5486</v>
+        <v>-0.6381</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1818</v>
+        <v>0.1064</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.2702</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.0422</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. MARTINEZ FERNANDEZ</t>
+          <t>D. TRUEBA TAMAYO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.5171</v>
+        <v>-0.411</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5537</v>
+        <v>-0.2907</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.0708</v>
+        <v>-0.1203</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.7452</v>
+        <v>-0.5819</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.174</v>
+        <v>0.0921</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5712</v>
+        <v>-0.674</v>
       </c>
       <c r="J4" t="n">
-        <v>1.3429</v>
+        <v>0.326</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.0002</v>
+        <v>0.9936</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3431</v>
+        <v>-0.6676</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.0881</v>
+        <v>-0.9079</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1738</v>
+        <v>-0.9014</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.9143</v>
+        <v>-0.0064</v>
       </c>
       <c r="P4" t="n">
-        <v>0.579</v>
+        <v>-0.386</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.965</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5441</v>
+        <v>0.579</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2631</v>
+        <v>0.5569</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5619</v>
+        <v>0.3483</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2988</v>
+        <v>0.2085</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.614</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>H. SAIZ-BUSTAMANTE GOMEZ</t>
+          <t>S. MARTINEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.8133</v>
+        <v>-0.651</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.442</v>
+        <v>1.3127</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6287</v>
+        <v>-1.9637</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.6631</v>
+        <v>-0.7452</v>
       </c>
       <c r="H5" t="n">
-        <v>2.4332</v>
+        <v>-0.174</v>
       </c>
       <c r="I5" t="n">
-        <v>-4.0963</v>
+        <v>-0.5712</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.6228</v>
+        <v>1.3429</v>
       </c>
       <c r="K5" t="n">
-        <v>2.6338</v>
+        <v>-0.0002</v>
       </c>
       <c r="L5" t="n">
-        <v>-3.2566</v>
+        <v>1.3431</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.0403</v>
+        <v>-2.0881</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2006</v>
+        <v>-0.1738</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8397</v>
+        <v>-1.9143</v>
       </c>
       <c r="P5" t="n">
-        <v>0.965</v>
+        <v>0.579</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9301</v>
+        <v>-0.965</v>
       </c>
       <c r="R5" t="n">
-        <v>2.8951</v>
+        <v>1.5441</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.3854</v>
+        <v>0.1292</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.117</v>
+        <v>0.3209</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2684</v>
+        <v>-0.1917</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2702</v>
+        <v>-0.614</v>
       </c>
       <c r="W5" t="n">
-        <v>1.228</v>
+        <v>0.614</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0422</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.0603</v>
+        <v>-1.0728</v>
       </c>
       <c r="E6" t="n">
-        <v>-5.7407</v>
+        <v>-4.78</v>
       </c>
       <c r="F6" t="n">
-        <v>3.6804</v>
+        <v>3.7072</v>
       </c>
       <c r="G6" t="n">
         <v>-4.3509</v>
@@ -922,13 +922,13 @@
         <v>3.8602</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9326</v>
+        <v>0.0549</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.7251</v>
+        <v>-0.7644</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7925</v>
+        <v>0.8193</v>
       </c>
       <c r="V6" t="n">
         <v>0.3281</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.2638</v>
+        <v>-1.3566</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.8379</v>
+        <v>-3.1181</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5741</v>
+        <v>1.7615</v>
       </c>
       <c r="G7" t="n">
         <v>-3.832</v>
@@ -1000,13 +1000,13 @@
         <v>2.1231</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.123</v>
+        <v>-0.2158</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.0708</v>
+        <v>-0.351</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0522</v>
+        <v>0.1352</v>
       </c>
       <c r="V7" t="n">
         <v>2.4982</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.3965</v>
+        <v>-2.6979</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.2474</v>
+        <v>-2.3882</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1491</v>
+        <v>-0.3097</v>
       </c>
       <c r="G8" t="n">
         <v>-1.1062</v>
@@ -1078,13 +1078,13 @@
         <v>2.1231</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2935</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5221</v>
+        <v>-0.6629</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8156</v>
+        <v>0.655</v>
       </c>
       <c r="V8" t="n">
         <v>-2.7418</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. CARCOBA BEDIA</t>
+          <t>D. GARCIA CARRERA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.3144</v>
+        <v>-3.2169</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.8936</v>
+        <v>-3.694</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5792</v>
+        <v>0.4771</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.3501</v>
+        <v>-5.2312</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.9238</v>
+        <v>-1.9489</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4263</v>
+        <v>-3.2823</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.7751</v>
+        <v>-3.4434</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.1075</v>
+        <v>-1.4078</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6676</v>
+        <v>-2.0356</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.575</v>
+        <v>-1.7878</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.8163</v>
+        <v>-0.5411</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2413</v>
+        <v>-1.2467</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.965</v>
+        <v>3.0881</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.8951</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.9301</v>
+        <v>3.0881</v>
       </c>
       <c r="S9" t="n">
-        <v>1.0007</v>
+        <v>-0.7879</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2049</v>
+        <v>-0.8645</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7958</v>
+        <v>0.0766</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5717</v>
+        <v>0.614</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5717</v>
+        <v>-0.8999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. GARCIA CARRERA</t>
+          <t>M. CARCOBA BEDIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.3511</v>
+        <v>-3.7507</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.614</v>
+        <v>-4.1157</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2629</v>
+        <v>0.365</v>
       </c>
       <c r="G10" t="n">
-        <v>-5.2312</v>
+        <v>-3.3501</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.9489</v>
+        <v>-2.9238</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.2823</v>
+        <v>-0.4263</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.4434</v>
+        <v>-1.7751</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.4078</v>
+        <v>-1.1075</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.0356</v>
+        <v>-0.6676</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.7878</v>
+        <v>-1.575</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5411</v>
+        <v>-1.8163</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.2467</v>
+        <v>0.2413</v>
       </c>
       <c r="P10" t="n">
-        <v>3.0881</v>
+        <v>-0.965</v>
       </c>
       <c r="Q10" t="n">
+        <v>-2.8951</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.9301</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.5645</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-0.0172</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.5816</v>
+      </c>
+      <c r="V10" t="n">
         <v>0</v>
       </c>
-      <c r="R10" t="n">
-        <v>3.0881</v>
-      </c>
-      <c r="S10" t="n">
-        <v>-1.9221</v>
-      </c>
-      <c r="T10" t="n">
-        <v>-1.7846</v>
-      </c>
-      <c r="U10" t="n">
-        <v>-0.1375</v>
-      </c>
-      <c r="V10" t="n">
-        <v>-0.2859</v>
-      </c>
       <c r="W10" t="n">
-        <v>0.614</v>
+        <v>0.5717</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.8999</v>
+        <v>-0.5717</v>
       </c>
     </row>
     <row r="11">
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.124099999999999</v>
+        <v>-1.2319</v>
       </c>
       <c r="E11" t="n">
-        <v>-10.7827</v>
+        <v>-9.890500000000001</v>
       </c>
       <c r="F11" t="n">
         <v>8.6585</v>
@@ -1285,10 +1285,10 @@
         <v>-15.5478</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.503199999999999</v>
+        <v>-2.5032</v>
       </c>
       <c r="K11" t="n">
-        <v>7.414200000000001</v>
+        <v>7.414199999999999</v>
       </c>
       <c r="L11" t="n">
         <v>-9.9175</v>
@@ -1297,7 +1297,7 @@
         <v>-12.1755</v>
       </c>
       <c r="N11" t="n">
-        <v>-6.5452</v>
+        <v>-6.545199999999999</v>
       </c>
       <c r="O11" t="n">
         <v>-5.6301</v>
@@ -1312,10 +1312,10 @@
         <v>22.196</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.006400000000000183</v>
+        <v>0.8857999999999997</v>
       </c>
       <c r="T11" t="n">
-        <v>-3.5888</v>
+        <v>-2.6966</v>
       </c>
       <c r="U11" t="n">
         <v>3.5823</v>
@@ -1324,10 +1324,10 @@
         <v>2.910700000000001</v>
       </c>
       <c r="W11" t="n">
-        <v>7.855099999999999</v>
+        <v>7.8551</v>
       </c>
       <c r="X11" t="n">
-        <v>-4.944399999999999</v>
+        <v>-4.9444</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.4224</v>
+        <v>5.6633</v>
       </c>
       <c r="E12" t="n">
         <v>3.3878</v>
       </c>
       <c r="F12" t="n">
-        <v>2.0346</v>
+        <v>2.2755</v>
       </c>
       <c r="G12" t="n">
         <v>3.9582</v>
@@ -1390,13 +1390,13 @@
         <v>0.772</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1011</v>
+        <v>0.3421</v>
       </c>
       <c r="T12" t="n">
         <v>-0.5063</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6074000000000001</v>
+        <v>0.8484</v>
       </c>
       <c r="V12" t="n">
         <v>1.5561</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.3983</v>
+        <v>2.3319</v>
       </c>
       <c r="E13" t="n">
-        <v>2.7848</v>
+        <v>2.5845</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3864</v>
+        <v>-0.2526</v>
       </c>
       <c r="G13" t="n">
         <v>3.9842</v>
@@ -1468,13 +1468,13 @@
         <v>1.7371</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4158</v>
+        <v>-0.4822</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3398</v>
+        <v>0.1395</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7554999999999999</v>
+        <v>-0.6217</v>
       </c>
       <c r="V13" t="n">
         <v>-1.5561</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.7888</v>
+        <v>2.1497</v>
       </c>
       <c r="E14" t="n">
-        <v>1.147</v>
+        <v>1.3472</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6418</v>
+        <v>0.8025</v>
       </c>
       <c r="G14" t="n">
         <v>1.0736</v>
@@ -1546,13 +1546,13 @@
         <v>1.7371</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8289</v>
+        <v>-0.468</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3278</v>
+        <v>-0.1276</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.501</v>
+        <v>-0.3404</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I. ECHEONDO LACALLE</t>
+          <t>M. BIDAURRE SOLA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2393</v>
+        <v>1.7741</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7916</v>
+        <v>-0.4803</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4477</v>
+        <v>2.2543</v>
       </c>
       <c r="G15" t="n">
-        <v>1.1613</v>
+        <v>5.718</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1397</v>
+        <v>1.3518</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3009</v>
+        <v>4.3662</v>
       </c>
       <c r="J15" t="n">
-        <v>1.208</v>
+        <v>4.1357</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4347</v>
+        <v>1.0918</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7733</v>
+        <v>3.0439</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0467</v>
+        <v>1.5823</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5743</v>
+        <v>0.26</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5276999999999999</v>
+        <v>1.3223</v>
       </c>
       <c r="P15" t="n">
-        <v>0.579</v>
+        <v>-3.4741</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.193</v>
+        <v>-4.8252</v>
       </c>
       <c r="R15" t="n">
-        <v>0.772</v>
+        <v>1.3511</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.501</v>
+        <v>0.1864</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2234</v>
+        <v>-0.6484</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2776</v>
+        <v>0.8348</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-0.6562</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.8576</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. BIDAURRE SOLA</t>
+          <t>I. ECHEONDO LACALLE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.199</v>
+        <v>1.1322</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.6806</v>
+        <v>0.7916</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8796</v>
+        <v>0.3406</v>
       </c>
       <c r="G16" t="n">
-        <v>5.718</v>
+        <v>1.1613</v>
       </c>
       <c r="H16" t="n">
-        <v>1.3518</v>
+        <v>-0.1397</v>
       </c>
       <c r="I16" t="n">
-        <v>4.3662</v>
+        <v>1.3009</v>
       </c>
       <c r="J16" t="n">
-        <v>4.1357</v>
+        <v>1.208</v>
       </c>
       <c r="K16" t="n">
-        <v>1.0918</v>
+        <v>0.4347</v>
       </c>
       <c r="L16" t="n">
-        <v>3.0439</v>
+        <v>0.7733</v>
       </c>
       <c r="M16" t="n">
-        <v>1.5823</v>
+        <v>-0.0467</v>
       </c>
       <c r="N16" t="n">
-        <v>0.26</v>
+        <v>-0.5743</v>
       </c>
       <c r="O16" t="n">
-        <v>1.3223</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>-3.4741</v>
+        <v>0.579</v>
       </c>
       <c r="Q16" t="n">
-        <v>-4.8252</v>
+        <v>-0.193</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3511</v>
+        <v>0.772</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3887</v>
+        <v>-0.6081</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8487</v>
+        <v>-0.2234</v>
       </c>
       <c r="U16" t="n">
-        <v>0.46</v>
+        <v>-0.3847</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6562</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.8576</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.5138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6469</v>
+        <v>0.7143</v>
       </c>
       <c r="E17" t="n">
-        <v>0.991</v>
+        <v>0.7907</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3441</v>
+        <v>-0.0764</v>
       </c>
       <c r="G17" t="n">
         <v>1.3346</v>
@@ -1780,13 +1780,13 @@
         <v>0.579</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1772</v>
+        <v>0.2446</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2803</v>
+        <v>0.08</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1031</v>
+        <v>0.1646</v>
       </c>
       <c r="V17" t="n">
         <v>-0.2859</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6153</v>
+        <v>0.6758</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.4902</v>
+        <v>-1.5904</v>
       </c>
       <c r="F18" t="n">
-        <v>2.1056</v>
+        <v>2.2662</v>
       </c>
       <c r="G18" t="n">
         <v>0.2077</v>
@@ -1858,13 +1858,13 @@
         <v>1.3511</v>
       </c>
       <c r="S18" t="n">
-        <v>0.345</v>
+        <v>0.4055</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1956</v>
+        <v>-0.2958</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5406</v>
+        <v>0.7013</v>
       </c>
       <c r="V18" t="n">
         <v>1.7997</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. SAVITSKI SAVITSKAIA</t>
+          <t>J. ARRIAZU ARBIZU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1759</v>
+        <v>-1.021</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.7579</v>
+        <v>-3.1271</v>
       </c>
       <c r="F19" t="n">
-        <v>2.582</v>
+        <v>2.106</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2101</v>
+        <v>-0.9507</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.7028</v>
+        <v>-1.6932</v>
       </c>
       <c r="I19" t="n">
-        <v>1.9129</v>
+        <v>0.7426</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.037</v>
+        <v>-1.5179</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.7611</v>
+        <v>-0.9317</v>
       </c>
       <c r="L19" t="n">
-        <v>0.724</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2471</v>
+        <v>0.5672</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9417</v>
+        <v>-0.7616000000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>1.1888</v>
+        <v>1.3288</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.579</v>
+        <v>-1.158</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.3161</v>
+        <v>-1.9301</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7371</v>
+        <v>0.772</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8441</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0766</v>
+        <v>-0.8226</v>
       </c>
       <c r="U19" t="n">
-        <v>0.8837</v>
+        <v>1.6666</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.614</v>
+        <v>0.2436</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3281</v>
+        <v>1.1435</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2859</v>
+        <v>-0.8999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. ARRIAZU ARBIZU</t>
+          <t>A. SAVITSKI SAVITSKAIA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5054999999999999</v>
+        <v>-1.0523</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.2272</v>
+        <v>-2.858</v>
       </c>
       <c r="F20" t="n">
-        <v>2.7217</v>
+        <v>1.8057</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.9507</v>
+        <v>0.2101</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.6932</v>
+        <v>-1.7028</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7426</v>
+        <v>1.9129</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.5179</v>
+        <v>-0.037</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.9317</v>
+        <v>-0.7611</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5862000000000001</v>
+        <v>0.724</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5672</v>
+        <v>0.2471</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7616000000000001</v>
+        <v>-0.9417</v>
       </c>
       <c r="O20" t="n">
-        <v>1.3288</v>
+        <v>1.1888</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.158</v>
+        <v>-0.579</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9301</v>
+        <v>-2.3161</v>
       </c>
       <c r="R20" t="n">
-        <v>0.772</v>
+        <v>1.7371</v>
       </c>
       <c r="S20" t="n">
-        <v>1.3596</v>
+        <v>-0.0694</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9227</v>
+        <v>-0.1768</v>
       </c>
       <c r="U20" t="n">
-        <v>2.2823</v>
+        <v>0.1074</v>
       </c>
       <c r="V20" t="n">
-        <v>0.2436</v>
+        <v>-0.614</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1435</v>
+        <v>-0.3281</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.8999</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.4765</v>
+        <v>-4.5033</v>
       </c>
       <c r="E21" t="n">
         <v>-3.131</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3456</v>
+        <v>-1.3723</v>
       </c>
       <c r="G21" t="n">
         <v>-0.389</v>
@@ -2092,13 +2092,13 @@
         <v>0.386</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1805</v>
+        <v>-0.2072</v>
       </c>
       <c r="T21" t="n">
         <v>-0.4164</v>
       </c>
       <c r="U21" t="n">
-        <v>0.236</v>
+        <v>0.2092</v>
       </c>
       <c r="V21" t="n">
         <v>-2.1701</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.0279</v>
+        <v>-5.7404</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.4738</v>
+        <v>-6.3736</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4458</v>
+        <v>0.6332</v>
       </c>
       <c r="G22" t="n">
         <v>-1.6292</v>
@@ -2170,13 +2170,13 @@
         <v>1.3511</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4686</v>
+        <v>-0.1811</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6848</v>
+        <v>-0.5846</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2161</v>
+        <v>0.4035</v>
       </c>
       <c r="V22" t="n">
         <v>-1.228</v>
@@ -2203,10 +2203,10 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>2.124200000000001</v>
+        <v>2.1243</v>
       </c>
       <c r="E23" t="n">
-        <v>-8.658499999999998</v>
+        <v>-8.6586</v>
       </c>
       <c r="F23" t="n">
         <v>10.7827</v>
@@ -2215,7 +2215,7 @@
         <v>14.6788</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.8690000000000001</v>
+        <v>-0.8689999999999999</v>
       </c>
       <c r="I23" t="n">
         <v>15.5478</v>
@@ -2233,13 +2233,13 @@
         <v>2.5032</v>
       </c>
       <c r="N23" t="n">
-        <v>-7.414300000000001</v>
+        <v>-7.414299999999999</v>
       </c>
       <c r="O23" t="n">
-        <v>9.917699999999998</v>
+        <v>9.9177</v>
       </c>
       <c r="P23" t="n">
-        <v>-9.650299999999998</v>
+        <v>-9.6503</v>
       </c>
       <c r="Q23" t="n">
         <v>-22.1959</v>
@@ -2248,22 +2248,22 @@
         <v>12.5456</v>
       </c>
       <c r="S23" t="n">
-        <v>0.006400000000000183</v>
+        <v>0.006700000000000067</v>
       </c>
       <c r="T23" t="n">
-        <v>-3.5822</v>
+        <v>-3.5824</v>
       </c>
       <c r="U23" t="n">
-        <v>3.588900000000001</v>
+        <v>3.589</v>
       </c>
       <c r="V23" t="n">
         <v>-2.9109</v>
       </c>
       <c r="W23" t="n">
-        <v>4.9444</v>
+        <v>4.944399999999999</v>
       </c>
       <c r="X23" t="n">
-        <v>-7.855199999999999</v>
+        <v>-7.8552</v>
       </c>
     </row>
   </sheetData>
